--- a/data/trans_dic/P22$ss-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,84; 97,55</t>
+          <t>94,87; 97,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>94,34; 97,73</t>
+          <t>94,37; 97,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,35; 98,26</t>
+          <t>95,3; 98,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95,85; 98,46</t>
+          <t>95,9; 98,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,57; 96,77</t>
+          <t>93,71; 96,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,56; 99,55</t>
+          <t>97,77; 99,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,43; 99,33</t>
+          <t>97,45; 99,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>97,95; 99,16</t>
+          <t>97,94; 99,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,8; 96,98</t>
+          <t>94,85; 96,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96,5; 98,45</t>
+          <t>96,57; 98,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96,82; 98,57</t>
+          <t>96,87; 98,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,29; 98,69</t>
+          <t>97,21; 98,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,22; 97,59</t>
+          <t>95,02; 97,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,57; 96,71</t>
+          <t>93,39; 96,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,88; 95,93</t>
+          <t>92,6; 95,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95,91; 98,71</t>
+          <t>96,0; 98,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,42; 97,04</t>
+          <t>94,34; 96,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,56; 98,44</t>
+          <t>96,42; 98,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,43; 98,34</t>
+          <t>96,45; 98,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>95,86; 97,65</t>
+          <t>95,82; 97,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,17; 96,96</t>
+          <t>95,09; 96,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95,42; 97,3</t>
+          <t>95,46; 97,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95,04; 96,81</t>
+          <t>94,98; 96,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,33; 98,07</t>
+          <t>96,34; 98,16</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,74; 97,13</t>
+          <t>93,54; 96,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92,37; 96,25</t>
+          <t>91,99; 96,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,02; 98,52</t>
+          <t>96,2; 98,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93,11; 97,44</t>
+          <t>93,34; 97,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,16; 96,44</t>
+          <t>93,29; 96,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,78; 95,68</t>
+          <t>91,76; 95,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,32; 97,2</t>
+          <t>94,25; 97,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,6; 98,92</t>
+          <t>96,52; 98,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93,98; 96,37</t>
+          <t>94,04; 96,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92,57; 95,43</t>
+          <t>92,73; 95,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95,81; 97,59</t>
+          <t>95,68; 97,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>95,84; 98,11</t>
+          <t>95,82; 98,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>92,8; 95,81</t>
+          <t>92,99; 95,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,31; 96,31</t>
+          <t>93,25; 96,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,7; 94,3</t>
+          <t>90,57; 94,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,02; 96,55</t>
+          <t>93,9; 96,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,76; 96,51</t>
+          <t>93,76; 96,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,73; 96,44</t>
+          <t>93,6; 96,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,85; 95,92</t>
+          <t>93,04; 95,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,18; 96,75</t>
+          <t>94,2; 96,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,95; 95,83</t>
+          <t>93,96; 95,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94,01; 95,97</t>
+          <t>93,98; 96,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92,41; 94,66</t>
+          <t>92,49; 94,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,65; 96,41</t>
+          <t>94,62; 96,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,93; 96,41</t>
+          <t>95,02; 96,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,31; 95,94</t>
+          <t>94,45; 96,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,27; 95,92</t>
+          <t>94,34; 95,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95,78; 97,37</t>
+          <t>95,77; 97,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,72; 96,16</t>
+          <t>94,67; 96,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,61; 97,01</t>
+          <t>95,6; 97,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,87; 97,12</t>
+          <t>95,75; 97,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>96,47; 97,7</t>
+          <t>96,53; 97,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,06; 96,09</t>
+          <t>95,01; 96,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95,3; 96,31</t>
+          <t>95,28; 96,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95,25; 96,29</t>
+          <t>95,35; 96,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>96,34; 97,32</t>
+          <t>96,37; 97,39</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>656180; 674897</t>
+          <t>656370; 675803</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>663664; 687474</t>
+          <t>663852; 687558</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>642341; 661925</t>
+          <t>641980; 661566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>609049; 625641</t>
+          <t>609372; 625982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>643326; 665307</t>
+          <t>644229; 665755</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>680030; 693901</t>
+          <t>681486; 694044</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>655562; 668337</t>
+          <t>655692; 668287</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>661929; 670095</t>
+          <t>661817; 670413</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1307612; 1337761</t>
+          <t>1308361; 1337608</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1351476; 1378771</t>
+          <t>1352493; 1378539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1303618; 1327253</t>
+          <t>1304275; 1327365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1275703; 1294025</t>
+          <t>1274601; 1294004</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>914872; 937647</t>
+          <t>912938; 937723</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>951583; 983556</t>
+          <t>949762; 982553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>948761; 979914</t>
+          <t>945894; 979250</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1144115; 1177530</t>
+          <t>1145148; 1178284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>914393; 939766</t>
+          <t>913596; 939112</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>996627; 1016061</t>
+          <t>995233; 1016373</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1003815; 1023764</t>
+          <t>1004011; 1023784</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>918415; 935615</t>
+          <t>918097; 935930</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1836040; 1870569</t>
+          <t>1834483; 1871115</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1955364; 1993756</t>
+          <t>1956129; 1994759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1960234; 1996640</t>
+          <t>1958889; 1998691</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2072063; 2109494</t>
+          <t>2072348; 2111317</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>635158; 658168</t>
+          <t>633805; 657085</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>699839; 729216</t>
+          <t>696910; 727652</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>727585; 746499</t>
+          <t>728933; 746616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>656150; 686635</t>
+          <t>657739; 686735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>637100; 659486</t>
+          <t>637960; 660243</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>713301; 743571</t>
+          <t>713129; 744504</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>736712; 759252</t>
+          <t>736217; 759348</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>901609; 923312</t>
+          <t>900858; 923501</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1279421; 1312040</t>
+          <t>1280270; 1313279</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1420825; 1464650</t>
+          <t>1423227; 1463706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1474349; 1501675</t>
+          <t>1472299; 1502148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1569844; 1607098</t>
+          <t>1569533; 1606721</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>872188; 900561</t>
+          <t>873990; 900668</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>884374; 912780</t>
+          <t>883766; 911949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>849545; 883254</t>
+          <t>848240; 880880</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>871437; 894900</t>
+          <t>870274; 894752</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>972687; 1001199</t>
+          <t>972706; 1000971</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>985897; 1014485</t>
+          <t>984600; 1014743</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>969158; 1001147</t>
+          <t>971090; 1000237</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1028804; 1056876</t>
+          <t>1029088; 1057023</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1857700; 1894927</t>
+          <t>1857813; 1896547</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1879884; 1919027</t>
+          <t>1879188; 1921120</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1829972; 1874570</t>
+          <t>1831726; 1877903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1911250; 1946672</t>
+          <t>1910654; 1946501</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3104184; 3152618</t>
+          <t>3107381; 3153465</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3230977; 3286587</t>
+          <t>3235833; 3289280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3195178; 3251103</t>
+          <t>3197578; 3248907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3313703; 3368767</t>
+          <t>3313369; 3370348</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3198770; 3247499</t>
+          <t>3197097; 3246151</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3401956; 3451750</t>
+          <t>3401818; 3453496</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3392445; 3436861</t>
+          <t>3388285; 3433545</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3530609; 3575358</t>
+          <t>3532799; 3573450</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6319080; 6387327</t>
+          <t>6315493; 6383131</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6656193; 6726464</t>
+          <t>6654781; 6728209</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6599057; 6671207</t>
+          <t>6606123; 6671010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6859215; 6928461</t>
+          <t>6861345; 6933410</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$ss-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,87; 97,68</t>
+          <t>94,63; 97,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>94,37; 97,74</t>
+          <t>94,35; 97,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,3; 98,21</t>
+          <t>95,2; 98,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95,9; 98,51</t>
+          <t>95,82; 98,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,71; 96,84</t>
+          <t>93,62; 96,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,77; 99,57</t>
+          <t>97,47; 99,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,45; 99,32</t>
+          <t>97,35; 99,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>97,94; 99,21</t>
+          <t>97,95; 99,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,85; 96,97</t>
+          <t>94,72; 97,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96,57; 98,43</t>
+          <t>96,6; 98,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96,87; 98,58</t>
+          <t>96,81; 98,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,21; 98,69</t>
+          <t>97,27; 98,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,02; 97,6</t>
+          <t>95,17; 97,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,39; 96,62</t>
+          <t>93,61; 96,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,6; 95,86</t>
+          <t>92,75; 95,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96,0; 98,78</t>
+          <t>95,03; 97,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,34; 96,98</t>
+          <t>94,46; 97,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,42; 98,47</t>
+          <t>96,39; 98,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,45; 98,35</t>
+          <t>96,38; 98,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>95,82; 97,69</t>
+          <t>96,02; 97,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,09; 96,99</t>
+          <t>95,14; 97,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95,46; 97,35</t>
+          <t>95,41; 97,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94,98; 96,91</t>
+          <t>95,01; 96,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,34; 98,16</t>
+          <t>95,89; 97,48</t>
         </is>
       </c>
     </row>
@@ -944,27 +944,27 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>95,93%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,03%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,54; 96,97</t>
+          <t>93,7; 97,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,99; 96,04</t>
+          <t>92,01; 95,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,2; 98,54</t>
+          <t>96,43; 98,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93,34; 97,45</t>
+          <t>93,74; 97,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93,29; 96,55</t>
+          <t>93,09; 96,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,76; 95,8</t>
+          <t>91,81; 95,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,25; 97,21</t>
+          <t>94,31; 97,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,52; 98,94</t>
+          <t>95,97; 98,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,04; 96,46</t>
+          <t>93,97; 96,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92,73; 95,37</t>
+          <t>92,68; 95,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95,68; 97,62</t>
+          <t>95,71; 97,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>95,82; 98,09</t>
+          <t>95,59; 97,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>92,99; 95,83</t>
+          <t>92,96; 95,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,25; 96,22</t>
+          <t>93,36; 96,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,57; 94,05</t>
+          <t>90,7; 94,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,9; 96,54</t>
+          <t>93,62; 96,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,76; 96,49</t>
+          <t>93,86; 96,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,6; 96,47</t>
+          <t>93,38; 96,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,04; 95,83</t>
+          <t>93,0; 95,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,2; 96,76</t>
+          <t>94,19; 96,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,96; 95,91</t>
+          <t>93,92; 95,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,98; 96,07</t>
+          <t>94,03; 96,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92,49; 94,83</t>
+          <t>92,43; 94,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,62; 96,4</t>
+          <t>94,43; 96,17</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>95,02; 96,43</t>
+          <t>95,01; 96,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,45; 96,02</t>
+          <t>94,45; 96,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,34; 95,85</t>
+          <t>94,42; 95,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95,77; 97,41</t>
+          <t>95,38; 96,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,67; 96,12</t>
+          <t>94,7; 96,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,6; 97,05</t>
+          <t>95,58; 96,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,75; 97,03</t>
+          <t>95,83; 97,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>96,53; 97,64</t>
+          <t>96,42; 97,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,01; 96,03</t>
+          <t>95,04; 96,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95,28; 96,34</t>
+          <t>95,28; 96,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95,35; 96,29</t>
+          <t>95,37; 96,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>96,37; 97,39</t>
+          <t>96,11; 96,97</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>619393</t>
+          <t>672584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>667115</t>
+          <t>723781</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1286509</t>
+          <t>1396365</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>656370; 675803</t>
+          <t>654721; 674735</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>663852; 687558</t>
+          <t>663713; 687764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>641980; 661566</t>
+          <t>641295; 661265</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>609372; 625982</t>
+          <t>661858; 679870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>644229; 665755</t>
+          <t>643621; 666297</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>681486; 694044</t>
+          <t>679420; 693233</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>655692; 668287</t>
+          <t>654985; 667821</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>661817; 670413</t>
+          <t>718090; 726964</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1308361; 1337608</t>
+          <t>1306474; 1338232</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1352493; 1378539</t>
+          <t>1352834; 1378391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1304275; 1327365</t>
+          <t>1303456; 1325990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1274601; 1294004</t>
+          <t>1384887; 1404726</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1161277</t>
+          <t>1012242</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>928385</t>
+          <t>1038505</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2089662</t>
+          <t>2050747</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>912938; 937723</t>
+          <t>914425; 938244</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>949762; 982553</t>
+          <t>951977; 983796</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>945894; 979250</t>
+          <t>947464; 979108</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1145148; 1178284</t>
+          <t>996836; 1023645</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>913596; 939112</t>
+          <t>914728; 939474</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>995233; 1016373</t>
+          <t>994920; 1016320</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1004011; 1023784</t>
+          <t>1003291; 1022964</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>918097; 935930</t>
+          <t>1028178; 1046618</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1834483; 1871115</t>
+          <t>1835425; 1871928</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1956129; 1994759</t>
+          <t>1955014; 1994829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1958889; 1998691</t>
+          <t>1959636; 1997449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2072348; 2111317</t>
+          <t>2032715; 2066392</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675981</t>
+          <t>771973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>912399</t>
+          <t>789400</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1588381</t>
+          <t>1561372</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>633805; 657085</t>
+          <t>634917; 657634</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>696910; 727652</t>
+          <t>697113; 726980</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>728933; 746616</t>
+          <t>730657; 747062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>657739; 686735</t>
+          <t>752816; 783799</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>637960; 660243</t>
+          <t>636618; 660601</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>713129; 744504</t>
+          <t>713530; 743722</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>736217; 759348</t>
+          <t>736699; 758771</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>900858; 923501</t>
+          <t>779504; 796497</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1280270; 1313279</t>
+          <t>1279333; 1310830</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1423227; 1463706</t>
+          <t>1422506; 1466128</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1472299; 1502148</t>
+          <t>1472830; 1500971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1569533; 1606721</t>
+          <t>1544036; 1575527</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884214</t>
+          <t>941395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1045286</t>
+          <t>1067531</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1929500</t>
+          <t>2008925</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>873990; 900668</t>
+          <t>873742; 901144</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>883766; 911949</t>
+          <t>884791; 912829</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>848240; 880880</t>
+          <t>849517; 884338</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>870274; 894752</t>
+          <t>926859; 952670</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>972706; 1000971</t>
+          <t>973691; 1002092</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>984600; 1014743</t>
+          <t>982224; 1013540</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>971090; 1000237</t>
+          <t>970736; 999590</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1029088; 1057023</t>
+          <t>1052297; 1079671</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1857813; 1896547</t>
+          <t>1857012; 1896117</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1879188; 1921120</t>
+          <t>1880205; 1919673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1831726; 1877903</t>
+          <t>1830388; 1873479</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1910654; 1946501</t>
+          <t>1989899; 2026507</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3340866</t>
+          <t>3398193</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3553187</t>
+          <t>3619216</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6894053</t>
+          <t>7017410</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3107381; 3153465</t>
+          <t>3106908; 3151417</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3235833; 3289280</t>
+          <t>3235543; 3289252</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3197578; 3248907</t>
+          <t>3200247; 3250951</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3313369; 3370348</t>
+          <t>3369388; 3420935</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3197097; 3246151</t>
+          <t>3198295; 3247317</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3401818; 3453496</t>
+          <t>3401162; 3450549</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3388285; 3433545</t>
+          <t>3391242; 3434231</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3532799; 3573450</t>
+          <t>3599760; 3635232</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6315493; 6383131</t>
+          <t>6317930; 6390272</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6654781; 6728209</t>
+          <t>6654579; 6727068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6606123; 6671010</t>
+          <t>6607416; 6672500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6861345; 6933410</t>
+          <t>6983679; 7046356</t>
         </is>
       </c>
     </row>
